--- a/business_forms/010_free_brand_audit_request_form--business_forms.xlsx
+++ b/business_forms/010_free_brand_audit_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,36 +525,40 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Free Brand Audit Request Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>1. What type of business do you have?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>e.g., Marketing, Consulting, E-commerce</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>main_purpose</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>2. What is the main purpose of your free brand audit request?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,84 +570,96 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>business_description</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>3. Can you describe your business in a few sentences?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>communication_method</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>4. What is your preferred method of communication?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>e.g., email, phone, chat</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>update_frequency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>5. Are you interested in a one-time free brand audit or would you like to receive regular updates?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>e.g., weekly, bi-weekly</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>free_resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>6. Would you like to receive any free resources in addition to the audit report?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>e.g., e-book, webinar, checklist</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,12 +674,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>7. Do you have any specific questions or concerns about the free brand audit process?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,16 +697,120 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>experience_level</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>8. How would you rate your level of experience with branding and marketing?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>e.g., 1-5, 1-10</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>expected_outcome</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>9. What is your expected outcome from the free brand audit?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>e.g., improved brand reputation, increased sales</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>time_required</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10. How long do you expect the free brand audit process to take?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>paid_services</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11. Are you interested in paid services after the free brand audit?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>e.g., consulting, strategy sessions</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>additional_info</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12. Would you like to provide any additional information about yourself or your business?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -707,12 +827,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,102 +855,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>communication_method_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>business_forms</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Business Forms</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>communication_method_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>business_surveys</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Business Surveys</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>communication_method_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>marketing_forms</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marketing Forms</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>update_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>business_forms</t>
+          <t>one-time_free_brand_audit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Business Forms</t>
+          <t>One-time free brand audit</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>update_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>business_surveys</t>
+          <t>weekly_updates</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Business Surveys</t>
+          <t>Weekly updates</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>update_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>marketing_forms</t>
+          <t>bi-weekly_updates</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marketing Forms</t>
+          <t>Bi-weekly updates</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>free_resources_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>e-book</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>E-book</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>free_resources_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>webinar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>free_resources_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Checklist</t>
         </is>
       </c>
     </row>
